--- a/artfynd/A 20509-2026 artfynd.xlsx
+++ b/artfynd/A 20509-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>69681360</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603034.0578237663</v>
+        <v>603034</v>
       </c>
       <c r="R2" t="n">
-        <v>6648958.212112905</v>
+        <v>6648958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>69681455</v>
       </c>
       <c r="B3" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603046.2210964812</v>
+        <v>603046</v>
       </c>
       <c r="R3" t="n">
-        <v>6648917.970024409</v>
+        <v>6648918</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,19 +848,9 @@
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +877,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69681340</v>
+        <v>69681476</v>
       </c>
       <c r="B4" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stenvillan, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603015.2118495654</v>
+        <v>603031</v>
       </c>
       <c r="R4" t="n">
-        <v>6648950.171441609</v>
+        <v>6648948</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,24 +949,9 @@
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-10-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ca 4 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,54 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>69681476</v>
+        <v>69681340</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stenvillan, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603030.8268888702</v>
+        <v>603015</v>
       </c>
       <c r="R5" t="n">
-        <v>6648948.101938892</v>
+        <v>6648950</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,19 +1046,14 @@
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-10-13</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ca 4 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 20509-2026 artfynd.xlsx
+++ b/artfynd/A 20509-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681455</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,8 +1097,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69681340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>